--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - RODAR - Copia.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - RODAR - Copia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042DA6E1-BAD9-46CF-BB36-688BB197E518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07E104B2-DB9F-487A-9401-6473A36ED4BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="38">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,46 +51,97 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Recusa  Sicoob 07-07-2025</t>
-  </si>
-  <si>
-    <t>133152782</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Relatório de Recusa Sicoob 07.07.2025</t>
-  </si>
-  <si>
-    <t>133161727</t>
-  </si>
-  <si>
-    <t>133167754</t>
-  </si>
-  <si>
-    <t>133234477</t>
-  </si>
-  <si>
-    <t>133170961</t>
-  </si>
-  <si>
-    <t>133266340</t>
-  </si>
-  <si>
-    <t>133286589</t>
-  </si>
-  <si>
-    <t>133170615</t>
-  </si>
-  <si>
-    <t>131684554</t>
-  </si>
-  <si>
-    <t>133157927</t>
-  </si>
-  <si>
-    <t>133171320</t>
+    <t>Allianz - Cancelamento 08.07.2025</t>
+  </si>
+  <si>
+    <t>128334855</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Nup- Cancelamento 08.07.2025</t>
+  </si>
+  <si>
+    <t>133252700</t>
+  </si>
+  <si>
+    <t>128648908</t>
+  </si>
+  <si>
+    <t>133134399</t>
+  </si>
+  <si>
+    <t>133138328</t>
+  </si>
+  <si>
+    <t>128753265</t>
+  </si>
+  <si>
+    <t>133089947</t>
+  </si>
+  <si>
+    <t>131143316</t>
+  </si>
+  <si>
+    <t>133064664</t>
+  </si>
+  <si>
+    <t>128621102</t>
+  </si>
+  <si>
+    <t>133273878</t>
+  </si>
+  <si>
+    <t>133218728</t>
+  </si>
+  <si>
+    <t>128328216</t>
+  </si>
+  <si>
+    <t>133274281 </t>
+  </si>
+  <si>
+    <t>128380912</t>
+  </si>
+  <si>
+    <t>128304636</t>
+  </si>
+  <si>
+    <t>132927279</t>
+  </si>
+  <si>
+    <t>133263407</t>
+  </si>
+  <si>
+    <t>133064044</t>
+  </si>
+  <si>
+    <t>128472499</t>
+  </si>
+  <si>
+    <t>133293466</t>
+  </si>
+  <si>
+    <t>133147839</t>
+  </si>
+  <si>
+    <t>128422293</t>
+  </si>
+  <si>
+    <t>133311583</t>
+  </si>
+  <si>
+    <t>133228154</t>
+  </si>
+  <si>
+    <t>133178215</t>
+  </si>
+  <si>
+    <t>133309093</t>
+  </si>
+  <si>
+    <t>130406300</t>
   </si>
 </sst>
 </file>
@@ -497,7 +548,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -609,7 +660,7 @@
       <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -627,7 +678,7 @@
       <c r="C7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -645,7 +696,7 @@
       <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -681,7 +732,7 @@
       <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -726,24 +777,307 @@
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D13" s="6"/>
+      <c r="A13" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D14" s="6"/>
+      <c r="A14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D15" s="6"/>
+      <c r="A15" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D16" s="6"/>
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="4:6" x14ac:dyDescent="0.25">
-      <c r="D17" s="6"/>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D32" s="6"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
